--- a/Mass_update_AQUA/mass_update_AQUA_hierarchy_fix.xlsx
+++ b/Mass_update_AQUA/mass_update_AQUA_hierarchy_fix.xlsx
@@ -1423,7 +1423,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>a0R3g000006iyew</t>
+          <t>a0R3g000006iyeu</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA MRL DEV LIC</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543770</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1455,7 +1455,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>a0R3g000006iyex</t>
+          <t>a0R3g000006iyf0</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>a0R3g000006iyey</t>
+          <t>a0R3g000006iyf1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>a0R3g000006iyez</t>
+          <t>a0R3g000006iyew</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>a0R3g000006iyf0</t>
+          <t>a0R3g000006iyex</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1583,7 +1583,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>a0R3g000006iyf1</t>
+          <t>a0R3g000006iyey</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1615,7 +1615,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>a0R3g000006iyeu</t>
+          <t>a0R3g000006iyez</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1630,12 +1630,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AQUA MRL DEV LIC</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1543770</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>a0R6g00000F0J1o</t>
+          <t>a0R6g00000F0J1r</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA3.0BRACHY DEV LIC</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554715</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1743,7 +1743,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>a0R6g00000F0J1p</t>
+          <t>a0R6g00000F0J1o</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1775,7 +1775,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>a0R6g00000F0J1q</t>
+          <t>a0R6g00000F0J1p</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1807,7 +1807,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>a0R6g00000F0J1r</t>
+          <t>a0R6g00000F0J1q</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AQUA3.0BRACHY DEV LIC</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1554715</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2511,7 +2511,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>a0R3g000000b3I5</t>
+          <t>a0R0d000005jHYH</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2526,12 +2526,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>AQUA MRL DEV LIC</t>
+          <t>AQUA ADDITIONAL DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1543770</t>
+          <t>1517663</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2543,7 +2543,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>a0R0d000005jHYH</t>
+          <t>a0R0d000005jHYI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2575,7 +2575,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>a0R0d000005jHYI</t>
+          <t>a0R0d000005jHYJ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2607,7 +2607,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>a0R0d000005jHYJ</t>
+          <t>a0R0d000005jHYK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2639,7 +2639,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>a0R0d000005jHYK</t>
+          <t>a0R0d000005jHYL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2671,7 +2671,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>a0R0d000005jHYL</t>
+          <t>a0R0d000005jHYM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2703,7 +2703,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>a0R0d000005jHYM</t>
+          <t>a0R0d000005jHYN</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2735,7 +2735,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>a0R0d000005jHYN</t>
+          <t>a0R3g000000b3I5</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>AQUA ADDITIONAL DEVICE LICENSE</t>
+          <t>AQUA MRL DEV LIC</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1517663</t>
+          <t>1543770</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2799,7 +2799,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>a0R3g000000Tsiy</t>
+          <t>a0R3g000000Tsix</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2831,7 +2831,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>a0R3g000000Tsix</t>
+          <t>a0R3g000000Tsiy</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>a0R6g00000H2ta3</t>
+          <t>a0R3g000009bskG</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA3.0BRACHY DEV LIC</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554715</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3055,7 +3055,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>a0R3g000009bskC</t>
+          <t>a0R3g000009bskF</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3087,7 +3087,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>a0R3g000009bskD</t>
+          <t>a0R6g00000H2ta3</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3119,7 +3119,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>a0R3g000009bskE</t>
+          <t>a0R3g000009bskC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3151,7 +3151,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>a0R3g000009bskF</t>
+          <t>a0R3g000009bskD</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3183,7 +3183,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>a0R3g000009bskG</t>
+          <t>a0R3g000009bskE</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3198,12 +3198,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AQUA3.0BRACHY DEV LIC</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1554715</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3375,7 +3375,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>a0R3g0000083DZd</t>
+          <t>a0R3g0000083DZb</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3407,7 +3407,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>a0R3g0000083DZe</t>
+          <t>a0R3g0000083DZc</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3439,7 +3439,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>a0R3g0000083DZb</t>
+          <t>a0R3g0000083DZd</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3471,7 +3471,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>a0R3g0000083DZc</t>
+          <t>a0R3g0000083DZe</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3823,7 +3823,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>a0R3g000008JE9d</t>
+          <t>a0R3g000008JE9f</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>AQUA MRL DEV LIC</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1543770</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -3855,7 +3855,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>a0R3g000008JE9g</t>
+          <t>a0R3g000008JE9d</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA MRL DEV LIC</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543770</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -3887,7 +3887,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>a0R3g000008JE9f</t>
+          <t>a0R3g000008JE9g</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3902,12 +3902,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -3919,7 +3919,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>a0RQQ00000GvuPs</t>
+          <t>a0RQQ00000GvuPt</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3934,12 +3934,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>C#89526</t>
+          <t>C#89528</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -3951,7 +3951,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>a0RQQ00000GvuPt</t>
+          <t>a0RQQ00000GvuPs</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>C#89528</t>
+          <t>C#89526</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -3983,7 +3983,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>a0R3g000008qtsn</t>
+          <t>a0R3g000000acQj</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>AQUA MRL DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1554714</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4015,7 +4015,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>a0R3g000000acQj</t>
+          <t>a0R3g000008qtsm</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4047,7 +4047,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>a0R3g000008qtsm</t>
+          <t>a0R3g000008qtsn</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA MRL DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1554714</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4079,7 +4079,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>a0R3g000000ajm2</t>
+          <t>a0R3g000000ajm0</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4094,12 +4094,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4111,7 +4111,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>a0R3g000000ajm3</t>
+          <t>a0R3g000000ajm1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4143,7 +4143,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>a0R3g000000ajm0</t>
+          <t>a0R3g000000ajm2</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4175,7 +4175,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>a0R3g000000ajm1</t>
+          <t>a0R3g000000ajm3</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4399,7 +4399,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>a0R3g000000TW64</t>
+          <t>a0R3g000000TW5u</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA MRL DEV LIC</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543770</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4431,7 +4431,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>a0R3g000000TW5u</t>
+          <t>a0R3g000000TW64</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>AQUA MRL DEV LIC</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>1543770</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4623,7 +4623,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>a0R6g00000EW8gz</t>
+          <t>a0R3g000008oaCg</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA MRL DEV LIC</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1543770</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -4655,7 +4655,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>a0R3g000008oaCg</t>
+          <t>a0R6g00000EW8gz</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>AQUA MRL DEV LIC</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>1543770</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -4719,7 +4719,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>a0R3g000009Sw0E</t>
+          <t>a0R3g000009Sw0F</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4734,12 +4734,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -4751,7 +4751,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>a0R3g000009Sw0F</t>
+          <t>a0R3g000009Sw0E</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4766,12 +4766,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -4783,7 +4783,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>a0R3g000000TsNi</t>
+          <t>a0R32000005dC4V</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA ADDITIONAL DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1517663</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -4815,7 +4815,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>a0R32000005dC4V</t>
+          <t>a0R32000005dKgP</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4847,7 +4847,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>a0R32000005dKgP</t>
+          <t>a0R3g000000TsNi</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>AQUA ADDITIONAL DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>1517663</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5039,7 +5039,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>a0R3g000007tOw5</t>
+          <t>a0R3g000007tOw3</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5071,7 +5071,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>a0R3g000007tOw6</t>
+          <t>a0R3g000007tOw4</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5103,7 +5103,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>a0R3g000007tOw3</t>
+          <t>a0R3g000007tOw5</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5135,7 +5135,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>a0R3g000007tOw4</t>
+          <t>a0R3g000007tOw6</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5231,7 +5231,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>a0R6g00000HfKZE</t>
+          <t>a0R3g000000UPtu</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5263,7 +5263,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>a0R3g000000UPtu</t>
+          <t>a0R6g00000HfKZE</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5519,7 +5519,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>a0R6g00000DLNFD</t>
+          <t>a0R6g00000DLNFE</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -5551,7 +5551,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>a0R6g00000DLNFE</t>
+          <t>a0R6g00000DLNFD</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -5647,7 +5647,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>a0R3g000009R4Bw</t>
+          <t>a0R3g000009R4By</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5662,12 +5662,12 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -5679,7 +5679,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>a0R3g000009R4By</t>
+          <t>a0R3g000009R4Bw</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -5871,7 +5871,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>a0R3g000000UH8S</t>
+          <t>a0R3g000000UH8T</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5903,7 +5903,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>a0R3g000000UH8T</t>
+          <t>a0R3g000000UH8S</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -6511,7 +6511,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>a0R3g000000UNy1</t>
+          <t>a0R6g00000GtVYj</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -6543,7 +6543,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>a0R3g000000UNy2</t>
+          <t>a0R6g00000GtVYk</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6558,12 +6558,12 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA MRL DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1554714</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -6575,7 +6575,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>a0R3g000000UNy3</t>
+          <t>a0R3g000000UNy1</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6607,7 +6607,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>a0R3g000000UNy4</t>
+          <t>a0R3g000000UNy2</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6639,7 +6639,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>a0R6g00000GtVYk</t>
+          <t>a0R3g000000UNy3</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>AQUA MRL DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>1554714</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -6671,7 +6671,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>a0R6g00000GtVYj</t>
+          <t>a0R3g000000UNy4</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -6991,7 +6991,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>a0R3g000008AJqh</t>
+          <t>a0R3g000008AJqe</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -7006,12 +7006,12 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -7023,7 +7023,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>a0R3g000008AJqi</t>
+          <t>a0R3g000008AJqf</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -7055,7 +7055,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>a0R3g000008AJqj</t>
+          <t>a0R3g000008AJqc</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA MRL DEV LIC</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543770</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -7087,7 +7087,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>a0R3g000008AJqk</t>
+          <t>a0R3g000008AJqg</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -7119,7 +7119,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>a0R3g000008AJqg</t>
+          <t>a0R3g000008AJqh</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -7151,7 +7151,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>a0R3g000008AJqc</t>
+          <t>a0R3g000008AJqi</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -7166,12 +7166,12 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>AQUA MRL DEV LIC</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>1543770</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -7183,7 +7183,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>a0R3g000008AJqe</t>
+          <t>a0R3g000008AJqj</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -7215,7 +7215,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>a0R3g000008AJqf</t>
+          <t>a0R3g000008AJqk</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -7279,7 +7279,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>a0R6g00000H0KEX</t>
+          <t>a0R6g00000H0KEZ</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -7311,7 +7311,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>a0R6g00000H0KEY</t>
+          <t>a0R6g00000H0KEX</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -7343,7 +7343,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>a0R6g00000H0KEZ</t>
+          <t>a0R6g00000H0KEY</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -7695,7 +7695,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>a0R6g00000H0E0U</t>
+          <t>a0R0d000006Zot0</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -7710,12 +7710,12 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA ADDITIONAL DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1517663</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -7727,7 +7727,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>a0R0d000006Zot0</t>
+          <t>a0R6g00000H0E0U</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>AQUA ADDITIONAL DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>1517663</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -7855,7 +7855,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>a0R3g000009R4Bx</t>
+          <t>a0R3g000009R4Bz</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA MRL DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554714</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -7887,7 +7887,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>a0R3g000009R4Bz</t>
+          <t>a0R3g000009R4Bx</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>AQUA MRL DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>1554714</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -7983,7 +7983,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>a0R6g00000HfD8T</t>
+          <t>a0R3g00000ACF5v</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -7998,12 +7998,12 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA MRL DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554714</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -8015,7 +8015,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>a0R3g00000ACF5v</t>
+          <t>a0R6g00000HfD8T</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>AQUA MRL DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>1554714</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -8111,7 +8111,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>a0RKf00000HpYQv</t>
+          <t>a0RKf00000HpYQw</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA BRACHY DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>C#89528</t>
+          <t>C#89529</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -8143,7 +8143,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>a0RKf00000HpYQw</t>
+          <t>a0RKf00000HpYQv</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -8158,12 +8158,12 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>AQUA BRACHY DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>C#89529</t>
+          <t>C#89528</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -8271,7 +8271,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>a0R3g00000AeO02</t>
+          <t>a0R3g00000AeO03</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -8303,7 +8303,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>a0R3g00000AeO03</t>
+          <t>a0R3g00000AeO02</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -8318,12 +8318,12 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -8463,7 +8463,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>a0R3g000008o1DK</t>
+          <t>a0R3g00000831dy</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA MRL DEV LIC</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543770</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -8495,7 +8495,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>a0R3g00000831dy</t>
+          <t>a0R3g000008o1DK</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>AQUA MRL DEV LIC</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>1543770</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -8559,7 +8559,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>a0R6g00000EUyNA</t>
+          <t>a0R3g000009cUxo</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -8574,12 +8574,12 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -8591,7 +8591,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>a0R3g000009cUxm</t>
+          <t>a0R3g000009cV5e</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA MRL DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554714</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -8623,7 +8623,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>a0R3g000009cUxn</t>
+          <t>a0R6g00000EUyNA</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -8655,7 +8655,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>a0R3g000009cUxo</t>
+          <t>a0R3g000009cUxm</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -8670,12 +8670,12 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -8687,7 +8687,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>a0R3g000009cV5e</t>
+          <t>a0R3g000009cUxn</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -8702,12 +8702,12 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>AQUA MRL DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>1554714</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -8815,7 +8815,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>a0R3g000000ayTq</t>
+          <t>a0R3g000000ayTp</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -8830,12 +8830,12 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -8847,7 +8847,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>a0R3g000000ayTp</t>
+          <t>a0R3g000000ayTq</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -8879,7 +8879,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>a0R3g0000069V8q</t>
+          <t>a0R3g000000UKCl</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>AQUA MRL DEV LIC</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>1543770</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -8911,7 +8911,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>a0R3g000000UJbL</t>
+          <t>a0R3g0000069V8q</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -8926,12 +8926,12 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA MRL DEV LIC</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543770</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -8943,7 +8943,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>a0R3g000000UKCl</t>
+          <t>a0R3g000000UJbL</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -8975,7 +8975,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>a0R0d000006TEaZ</t>
+          <t>a0R3g00000BLgLm</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -9007,7 +9007,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>a0R3g00000BLgLm</t>
+          <t>a0R0d000006TEaZ</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -9615,7 +9615,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>a0R3g000006jbsx</t>
+          <t>a0R3g000006jbsi</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -9630,12 +9630,12 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -9647,7 +9647,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>a0R3g000006jruE</t>
+          <t>a0R3g000006jbsx</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -9679,7 +9679,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>a0R3g000006jruF</t>
+          <t>a0R3g000006jruE</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -9711,7 +9711,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>a0R3g000006jruG</t>
+          <t>a0R3g000006jruF</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -9743,7 +9743,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>a0R3g000006jruH</t>
+          <t>a0R3g000006jruG</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -9775,7 +9775,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>a0R3g000006jbsi</t>
+          <t>a0R3g000006jruH</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -10447,7 +10447,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>a0R3g00000C5Kgr</t>
+          <t>a0R3g00000C5Kgs</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -10479,7 +10479,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>a0R3g00000C5Kgs</t>
+          <t>a0R3g00000C5Kgr</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -10494,12 +10494,12 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -10607,7 +10607,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>a0R6g00000HgHtx</t>
+          <t>a0R6g00000HgHty</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -10622,12 +10622,12 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>C#89526</t>
+          <t>C#89528</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -10639,7 +10639,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>a0R6g00000HgHty</t>
+          <t>a0R6g00000HgHtx</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -10654,12 +10654,12 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>C#89528</t>
+          <t>C#89526</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -10735,7 +10735,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>a0R3g000000Ta0Q</t>
+          <t>a0R0d000006ZwAQ</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -10750,12 +10750,12 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA ADDITIONAL DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1517663</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -10767,7 +10767,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>a0R3g000000Ta0R</t>
+          <t>a0R0d000006ZwAN</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -10782,12 +10782,12 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA ADDITIONAL DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1517663</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -10799,7 +10799,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>a0R3g000000Ta0S</t>
+          <t>a0R0d000006ZwAO</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA ADDITIONAL DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1517663</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -10831,7 +10831,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>a0R0d000006ZwAN</t>
+          <t>a0R0d000006ZwAP</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -10863,7 +10863,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>a0R0d000006ZwAO</t>
+          <t>a0R3g000000Ta0N</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -10878,12 +10878,12 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>AQUA ADDITIONAL DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>1517663</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -10895,7 +10895,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>a0R0d000006ZwAP</t>
+          <t>a0R3g000000Ta0O</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -10910,12 +10910,12 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>AQUA ADDITIONAL DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>1517663</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -10927,7 +10927,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>a0R0d000006ZwAQ</t>
+          <t>a0R3g000000Ta0P</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>AQUA ADDITIONAL DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>1517663</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -10959,7 +10959,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>a0R3g000000Ta0N</t>
+          <t>a0R3g000000Ta0Q</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -10974,12 +10974,12 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -10991,7 +10991,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>a0R3g000000Ta0O</t>
+          <t>a0R3g000000Ta0R</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -11023,7 +11023,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>a0R3g000000Ta0P</t>
+          <t>a0R3g000000Ta0S</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -11038,12 +11038,12 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -11439,7 +11439,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>a0R6g00000DLeki</t>
+          <t>a0R0d000006EZY1</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -11454,12 +11454,12 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA ADDITIONAL DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1517663</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -11471,7 +11471,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>a0R6g00000DLekj</t>
+          <t>a0R6g00000DLeki</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -11503,7 +11503,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>a0R6g00000DLekk</t>
+          <t>a0R6g00000DLekj</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -11535,7 +11535,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>a0R0d000006EZY1</t>
+          <t>a0R6g00000DLekk</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -11550,12 +11550,12 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>AQUA ADDITIONAL DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>1517663</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -11599,7 +11599,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>a0R3g000000an4k</t>
+          <t>a0R3g000000an4j</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -11614,12 +11614,12 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
@@ -11631,7 +11631,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>a0R3g000000an4l</t>
+          <t>a0R3g000000an4k</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -11663,7 +11663,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>a0R3g000000an4j</t>
+          <t>a0R3g000000an4l</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -11678,12 +11678,12 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
@@ -11727,7 +11727,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>a0R3g00000BNtTm</t>
+          <t>a0R3g00000BNtTt</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -11759,7 +11759,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>a0R3g00000BNtTn</t>
+          <t>a0R3g00000BNtTu</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -11774,12 +11774,12 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
@@ -11791,7 +11791,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>a0R3g00000BNtTt</t>
+          <t>a0R3g00000BNtTm</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -11806,12 +11806,12 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
@@ -11823,7 +11823,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>a0R3g00000BNtTu</t>
+          <t>a0R3g00000BNtTn</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -11838,12 +11838,12 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
@@ -11919,7 +11919,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>a0R3g000006jti0</t>
+          <t>a0R3g000006jthz</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -11951,7 +11951,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>a0R3g000006jti1</t>
+          <t>a0R3g000006jti0</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -11983,7 +11983,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>a0R3g000006jti2</t>
+          <t>a0R3g000006jti1</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -12015,7 +12015,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>a0R3g000006jthz</t>
+          <t>a0R3g000006jti2</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -12207,7 +12207,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>a0R6g00000HihDN</t>
+          <t>a0R6g00000Hib7B</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
@@ -12239,7 +12239,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>a0R6g00000Hib7B</t>
+          <t>a0R6g00000HihDN</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -12399,7 +12399,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>a0R6g00000EWCdi</t>
+          <t>a0R6g00000EWCdn</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -12431,7 +12431,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>a0R6g00000EWCdj</t>
+          <t>a0R6g00000EWCdi</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -12463,7 +12463,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>a0R6g00000EWCdk</t>
+          <t>a0R6g00000EWCdj</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -12495,7 +12495,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>a0R6g00000EWCdl</t>
+          <t>a0R6g00000EWCdk</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -12527,7 +12527,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>a0R6g00000EWCdn</t>
+          <t>a0R6g00000EWCdl</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
@@ -12591,7 +12591,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>a0R3g00000AYMux</t>
+          <t>a0R3g00000AYMuz</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -12606,12 +12606,12 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
@@ -12623,7 +12623,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>a0R3g00000AYMuy</t>
+          <t>a0R3g00000AYMux</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -12655,7 +12655,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>a0R3g00000AYMuz</t>
+          <t>a0R3g00000AYMuy</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -12670,12 +12670,12 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
@@ -12687,7 +12687,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>a0R0d000005zVvV</t>
+          <t>a0R0d000005zVvX</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -12719,7 +12719,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>a0R0d000005zVvW</t>
+          <t>a0R0d000005zVvY</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -12751,7 +12751,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>a0R0d000005zVvX</t>
+          <t>a0R0d000005zVvW</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -12783,7 +12783,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>a0R0d000005zVvY</t>
+          <t>a0R0d000005zVvV</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -12911,7 +12911,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>a0R3g000006lWqM</t>
+          <t>a0R3g000006lWqK</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -12926,12 +12926,12 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -12943,7 +12943,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>a0R3g000006lWqN</t>
+          <t>a0R3g000006lWqM</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -12975,7 +12975,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>a0R3g000006lWqK</t>
+          <t>a0R3g000006lWqN</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -12990,12 +12990,12 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
@@ -13103,7 +13103,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>a0R6g00000H0O3L</t>
+          <t>a0R6g00000H0O3M</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA3.0BRACHY DEV LIC</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554715</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
@@ -13135,7 +13135,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>a0R6g00000H0O3M</t>
+          <t>a0R6g00000H0O3L</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -13150,12 +13150,12 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>AQUA3.0BRACHY DEV LIC</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>1554715</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
@@ -13551,7 +13551,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>a0R6g00000F0boW</t>
+          <t>a0R6g00000F0boV</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -13566,12 +13566,12 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>AQUA MRL DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>1554714</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
@@ -13583,7 +13583,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>a0R6g00000F0boV</t>
+          <t>a0R6g00000F0boW</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -13598,12 +13598,12 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA MRL DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1554714</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
@@ -13807,7 +13807,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>a0R3g00000BOlki</t>
+          <t>a0R3g00000BOlkj</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -13822,12 +13822,12 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
@@ -13839,7 +13839,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>a0R3g00000BOlkj</t>
+          <t>a0R3g00000BOlki</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -13854,12 +13854,12 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
@@ -14287,7 +14287,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>a0R3g000006jugj</t>
+          <t>a0R3g000006jugi</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -14302,12 +14302,12 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
@@ -14351,7 +14351,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>a0R3g000006jugi</t>
+          <t>a0R3g000006jugj</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -14366,12 +14366,12 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
@@ -14383,7 +14383,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>a0R3g000008Lk8p</t>
+          <t>a0R3g000008Lk8n</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -14398,12 +14398,12 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -14415,7 +14415,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>a0R3g000008Lk8q</t>
+          <t>a0R3g000008Lk8p</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -14447,7 +14447,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>a0R3g000008Lk8n</t>
+          <t>a0R3g000008Lk8q</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -14462,12 +14462,12 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
@@ -14767,7 +14767,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>a0R3g000008BBkv</t>
+          <t>a0R3g000008BBkt</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -14782,12 +14782,12 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
@@ -14799,7 +14799,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>a0R3g000008BBkt</t>
+          <t>a0R3g000008BBkv</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -14814,12 +14814,12 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
@@ -15183,7 +15183,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>a0R3g000008re3n</t>
+          <t>a0R3g000008re25</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -15198,12 +15198,12 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
@@ -15215,7 +15215,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>a0R3g000008re25</t>
+          <t>a0R3g000008re3o</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -15230,12 +15230,12 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
@@ -15247,7 +15247,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>a0R3g000008re3o</t>
+          <t>a0R3g000008re3p</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -15279,7 +15279,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>a0R3g000008re3p</t>
+          <t>a0R3g000008re3q</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -15311,7 +15311,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>a0R3g000008re3q</t>
+          <t>a0R3g000008re3n</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -15439,7 +15439,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>a0R3g000000UPmb</t>
+          <t>a0R3g000000UPmd</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -15454,12 +15454,12 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>AQUA MRL DEV LIC</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>1543770</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
@@ -15471,7 +15471,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>a0R3g000000UPmd</t>
+          <t>a0R3g000000UPmb</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -15486,12 +15486,12 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA MRL DEV LIC</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1543770</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
@@ -15631,7 +15631,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>a0R3g0000067w8A</t>
+          <t>a0R3g0000067w8B</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -15663,7 +15663,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>a0R3g0000067w8B</t>
+          <t>a0R3g0000067w8A</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -15759,7 +15759,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>a0R6g00000H01Ec</t>
+          <t>a0R6g00000H01Ej</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -15774,12 +15774,12 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA3.0BRACHY DEV LIC</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554715</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
@@ -15791,7 +15791,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>a0R6g00000H01Ed</t>
+          <t>a0R6g00000H01Eg</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -15806,12 +15806,12 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
@@ -15823,7 +15823,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>a0R6g00000H01Ee</t>
+          <t>a0R6g00000H01Eh</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
@@ -15855,7 +15855,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>a0R6g00000H01Ef</t>
+          <t>a0R6g00000H01Ei</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -15870,12 +15870,12 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
@@ -15887,7 +15887,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>a0R6g00000H01Eg</t>
+          <t>a0R6g00000H01Ec</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -15902,12 +15902,12 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
@@ -15919,7 +15919,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>a0R6g00000H01Eh</t>
+          <t>a0R6g00000H01Ed</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -15934,12 +15934,12 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
@@ -15951,7 +15951,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>a0R6g00000H01Ei</t>
+          <t>a0R6g00000H01Ee</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -15966,12 +15966,12 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
@@ -15983,7 +15983,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>a0R6g00000H01Ej</t>
+          <t>a0R6g00000H01Ef</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -15998,12 +15998,12 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>AQUA3.0BRACHY DEV LIC</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>1554715</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
@@ -16335,7 +16335,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>a0R3g000000aTtC</t>
+          <t>a0R3g000000aTtG</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -16367,7 +16367,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>a0R3g000000aTtD</t>
+          <t>a0R3g000000aTtH</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -16399,7 +16399,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>a0R3g000000aTtE</t>
+          <t>a0R3g000000aTtI</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -16431,7 +16431,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>a0R3g000000aTtF</t>
+          <t>a0R3g000000aTtC</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -16463,7 +16463,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>a0R3g000000aTtG</t>
+          <t>a0R3g000000aTtD</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -16495,7 +16495,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>a0R3g000000aTtH</t>
+          <t>a0R3g000000aTtE</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -16527,7 +16527,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>a0R3g000000aTtI</t>
+          <t>a0R3g000000aTtF</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -16559,7 +16559,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>a0R3g000000U1lF</t>
+          <t>a0R3g000000U1lD</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
@@ -16591,7 +16591,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>a0R3g000000U1lG</t>
+          <t>a0R3g000000U1lE</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -16606,12 +16606,12 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F506" t="inlineStr">
@@ -16623,7 +16623,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>a0R3g000000U1lD</t>
+          <t>a0R3g000000U1lF</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -16638,12 +16638,12 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
@@ -16655,7 +16655,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>a0R3g000000U1lE</t>
+          <t>a0R3g000000U1lG</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -16670,12 +16670,12 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
@@ -16783,7 +16783,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>a0R6g00000EVvFE</t>
+          <t>a0R6g00000EVvFI</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -16798,12 +16798,12 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA3.0BRACHY DEV LIC</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554715</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
@@ -16847,7 +16847,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>a0R6g00000EVvFF</t>
+          <t>a0R6g00000EVvFE</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -16879,7 +16879,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>a0R6g00000EVvFG</t>
+          <t>a0R6g00000EVvFF</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -16911,7 +16911,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>a0R6g00000EVvFI</t>
+          <t>a0R6g00000EVvFG</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -16926,12 +16926,12 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>AQUA3.0BRACHY DEV LIC</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>1554715</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F516" t="inlineStr">
@@ -16943,7 +16943,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>a0R6g00000HfRa6</t>
+          <t>a0R6g00000HgO7b</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -16958,12 +16958,12 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA MRL DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554714</t>
         </is>
       </c>
       <c r="F517" t="inlineStr">
@@ -16975,7 +16975,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>a0R6g00000HgO7b</t>
+          <t>a0R6g00000HfRa6</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -16990,12 +16990,12 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>AQUA MRL DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>1554714</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
@@ -17263,7 +17263,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>a0R3g000007kqTH</t>
+          <t>a0R3g000007kqTI</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -17278,12 +17278,12 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="F527" t="inlineStr">
@@ -17295,7 +17295,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>a0R3g000007kqTI</t>
+          <t>a0R3g000007kqTH</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -17310,12 +17310,12 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F528" t="inlineStr">
@@ -17487,7 +17487,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>a0R6g00000H0LcA</t>
+          <t>a0R6g00000H0LcC</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -17502,12 +17502,12 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA3.0BRACHY DEV LIC</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554715</t>
         </is>
       </c>
       <c r="F534" t="inlineStr">
@@ -17519,7 +17519,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>a0R6g00000H0LcB</t>
+          <t>a0R6g00000H0LcA</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17551,7 +17551,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>a0R6g00000H0LcC</t>
+          <t>a0R6g00000H0LcB</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -17566,12 +17566,12 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>AQUA3.0BRACHY DEV LIC</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>1554715</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F536" t="inlineStr">
@@ -18255,7 +18255,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>a0R6g00000DLGlk</t>
+          <t>a0R0d000006a5Hi</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -18270,12 +18270,12 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA ADDITIONAL DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1517663</t>
         </is>
       </c>
       <c r="F558" t="inlineStr">
@@ -18287,7 +18287,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>a0R0d000006a5Hi</t>
+          <t>a0R6g00000DLGlk</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -18302,12 +18302,12 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>AQUA ADDITIONAL DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>1517663</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F559" t="inlineStr">
@@ -18639,7 +18639,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>a0R3g000006jlRr</t>
+          <t>a0R3g000006jlRp</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -18654,12 +18654,12 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA MRL DEV LIC</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543770</t>
         </is>
       </c>
       <c r="F570" t="inlineStr">
@@ -18671,7 +18671,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>a0R3g000006jlRp</t>
+          <t>a0R3g000006jlRr</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -18686,12 +18686,12 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>AQUA MRL DEV LIC</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>1543770</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F571" t="inlineStr">
@@ -18831,7 +18831,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>a0R3g00000BsbYG</t>
+          <t>a0R3g00000BsbYM</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -18846,12 +18846,12 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>AQUA MRL DEVICE LICENSE</t>
+          <t>AQUA3.0BRACHY DEV LIC</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>1554714</t>
+          <t>1554715</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
@@ -18863,7 +18863,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>a0R3g00000BsbYM</t>
+          <t>a0R3g00000BsbYG</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -18878,12 +18878,12 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>AQUA3.0BRACHY DEV LIC</t>
+          <t>AQUA MRL DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>1554715</t>
+          <t>1554714</t>
         </is>
       </c>
       <c r="F577" t="inlineStr">
@@ -18959,7 +18959,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>a0R3g00000BlyZs</t>
+          <t>a0R3g00000BlyZt</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -18974,12 +18974,12 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="F580" t="inlineStr">
@@ -18991,7 +18991,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>a0R3g00000BlyZt</t>
+          <t>a0R3g00000BlyZs</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F581" t="inlineStr">
@@ -19055,7 +19055,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>a0R3g000006jFIA</t>
+          <t>a0R3g000006jFI9</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -19070,12 +19070,12 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F583" t="inlineStr">
@@ -19087,7 +19087,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>a0R3g000006jFIB</t>
+          <t>a0R3g000006jFIA</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -19119,7 +19119,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>a0R3g000006jFI9</t>
+          <t>a0R3g000006jFIB</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F585" t="inlineStr">
@@ -19279,7 +19279,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>a0R3g000000USFX</t>
+          <t>a0R3g000000USFW</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -19294,12 +19294,12 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F590" t="inlineStr">
@@ -19311,7 +19311,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>a0R3g000000USFW</t>
+          <t>a0R3g000000USFX</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -19326,12 +19326,12 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F591" t="inlineStr">
@@ -19503,7 +19503,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>a0R3g000008mZiZ</t>
+          <t>a0R3g000008mZiX</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -19518,12 +19518,12 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F597" t="inlineStr">
@@ -19535,7 +19535,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>a0R3g000008mZiX</t>
+          <t>a0R3g000008mZiZ</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -19550,12 +19550,12 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F598" t="inlineStr">
@@ -19567,7 +19567,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>a0RKf00000Hp36H</t>
+          <t>a0RKf00000Hp36G</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -19582,12 +19582,12 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>1541636</t>
+          <t>1543771</t>
         </is>
       </c>
       <c r="F599" t="inlineStr">
@@ -19599,7 +19599,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>a0RKf00000Hp36G</t>
+          <t>a0RKf00000Hp36H</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -19614,12 +19614,12 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>1543771</t>
+          <t>1541636</t>
         </is>
       </c>
       <c r="F600" t="inlineStr">
@@ -19631,7 +19631,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>a0R6g00000HfncW</t>
+          <t>a0R3g0000081SDb</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -19646,12 +19646,12 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA MRL DEV LIC</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1543770</t>
         </is>
       </c>
       <c r="F601" t="inlineStr">
@@ -19663,7 +19663,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>a0R3g0000081SDb</t>
+          <t>a0R6g00000HfncW</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -19678,12 +19678,12 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>AQUA MRL DEV LIC</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>1543770</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F602" t="inlineStr">
@@ -20335,7 +20335,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>a0RKf00000JNssT</t>
+          <t>a0RKf00000JNssU</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -20350,12 +20350,12 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>AQUA MRL DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>C#89527</t>
+          <t>C#89528</t>
         </is>
       </c>
       <c r="F623" t="inlineStr">
@@ -20367,7 +20367,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>a0RKf00000JNssU</t>
+          <t>a0RKf00000JNssT</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -20382,12 +20382,12 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA MRL DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>C#89528</t>
+          <t>C#89527</t>
         </is>
       </c>
       <c r="F624" t="inlineStr">
@@ -20847,7 +20847,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>a0R6g00000DL8GQ</t>
+          <t>a0R6g00000DL8GR</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -20862,12 +20862,12 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="F639" t="inlineStr">
@@ -20879,7 +20879,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>a0R6g00000DL8GR</t>
+          <t>a0R6g00000DL8GQ</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -20894,12 +20894,12 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F640" t="inlineStr">
@@ -21199,7 +21199,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>a0R6g00000Hib8Y</t>
+          <t>a0R6g00000Hib8Z</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -21214,12 +21214,12 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>AQUA TREATMENT DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>1554712</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="F650" t="inlineStr">
@@ -21231,7 +21231,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>a0R6g00000Hib8Z</t>
+          <t>a0R6g00000Hib8Y</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
@@ -21246,12 +21246,12 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1554712</t>
         </is>
       </c>
       <c r="F651" t="inlineStr">
@@ -21391,7 +21391,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>a0RKf00000HqRd6</t>
+          <t>a0RKf00000HqRd5</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -21406,12 +21406,12 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>AQUA MRL DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>1554714</t>
+          <t>1554713</t>
         </is>
       </c>
       <c r="F656" t="inlineStr">
@@ -21423,7 +21423,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>a0RKf00000HqRd5</t>
+          <t>a0RKf00000HqRd6</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -21438,12 +21438,12 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA MRL DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>1554713</t>
+          <t>1554714</t>
         </is>
       </c>
       <c r="F657" t="inlineStr">
@@ -21487,7 +21487,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>a0RKf00000JNoRZ</t>
+          <t>a0RKf00000JNoRa</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -21502,12 +21502,12 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
+          <t>AQUA BRACHY DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>C#89528</t>
+          <t>C#89529</t>
         </is>
       </c>
       <c r="F659" t="inlineStr">
@@ -21519,7 +21519,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>a0RKf00000JNoRa</t>
+          <t>a0RKf00000JNoRZ</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -21534,12 +21534,12 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>AQUA BRACHY DEVICE LICENSE</t>
+          <t>AQUA DIAGNOSTIC DEVICE LICENSE</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>C#89529</t>
+          <t>C#89528</t>
         </is>
       </c>
       <c r="F660" t="inlineStr">

--- a/Mass_update_AQUA/mass_update_AQUA_hierarchy_fix.xlsx
+++ b/Mass_update_AQUA/mass_update_AQUA_hierarchy_fix.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,17 +463,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>a0RQQ00000LjGPV</t>
+          <t>a0RQQ00000MNZMz</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>a0RQQ00000LjGUL</t>
+          <t>a0RQQ00000MNaAz</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>a0RQQ00000LjGUL</t>
+          <t>a0RQQ00000MNaAz</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -488,24 +488,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19164_AQ001_2</t>
+          <t>10234_AQ001_2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>a0RQQ00000J7nXc</t>
+          <t>a0RQQ00000MCoUD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>a0RQQ00000LjGUL</t>
+          <t>a0RQQ00000MNaAz</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>a0RQQ00000LjGUL</t>
+          <t>a0RQQ00000MNaAz</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -520,39 +520,135 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19164_AQ001_2</t>
+          <t>10234_AQ001_2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>a0RQQ00000LjGPV</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>a0RQQ00000LjGUL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>a0RQQ00000LjGUL</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AQUA SOFTWARE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>C#89525-33</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>19164_AQ001_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>a0RQQ00000J7nXc</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>a0RQQ00000LjGUL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>a0RQQ00000LjGUL</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AQUA TREATMENT DEVICE LICENSE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>C#89526</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>19164_AQ001_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>a0RQQ00000J7nXa</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>a0RQQ00000Lgd2T</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>a0RQQ00000Lgd2T</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>AQUA TREATMENT DEVICE LICENSE</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>C#89526</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>30000548_AQ001_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>a0R3g000000UR0O</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>a0R6g00000DLIXW</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>a0R6g00000DLIXW</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AQUA MRL DEVICE LICENSE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1554714</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>30002692_AQU001_2</t>
         </is>
       </c>
     </row>
